--- a/artfynd/A 62373-2025 artfynd.xlsx
+++ b/artfynd/A 62373-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187611</v>
       </c>
       <c r="B2" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62373-2025 artfynd.xlsx
+++ b/artfynd/A 62373-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187611</v>
       </c>
       <c r="B2" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62373-2025 artfynd.xlsx
+++ b/artfynd/A 62373-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187611</v>
       </c>
       <c r="B2" t="n">
-        <v>93048</v>
+        <v>93051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62373-2025 artfynd.xlsx
+++ b/artfynd/A 62373-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187611</v>
       </c>
       <c r="B2" t="n">
-        <v>93051</v>
+        <v>93077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62373-2025 artfynd.xlsx
+++ b/artfynd/A 62373-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187611</v>
       </c>
       <c r="B2" t="n">
-        <v>93077</v>
+        <v>93078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62373-2025 artfynd.xlsx
+++ b/artfynd/A 62373-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187611</v>
       </c>
       <c r="B2" t="n">
-        <v>93078</v>
+        <v>93079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62373-2025 artfynd.xlsx
+++ b/artfynd/A 62373-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187611</v>
       </c>
       <c r="B2" t="n">
-        <v>93079</v>
+        <v>93081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62373-2025 artfynd.xlsx
+++ b/artfynd/A 62373-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187611</v>
       </c>
       <c r="B2" t="n">
-        <v>93081</v>
+        <v>93085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
